--- a/esyluban/examples/dev/DataTables/test/inline_defs.xlsx
+++ b/esyluban/examples/dev/DataTables/test/inline_defs.xlsx
@@ -857,7 +857,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>full_name="test.TbInlineEnum" &amp; value_type="test.InlineBean" &amp; index="id" &amp; mode="map" &amp; read_schema_from_file="false" &amp; output="test_tbinlineenum"</t>
+          <t>full_name="test.TbInlineEnum" &amp; value_type="test.InlineBean" &amp; index="id"</t>
         </is>
       </c>
     </row>

--- a/esyluban/examples/dev/DataTables/test/inline_defs.xlsx
+++ b/esyluban/examples/dev/DataTables/test/inline_defs.xlsx
@@ -591,7 +591,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="H1:L1"/>
+    <mergeCell ref="H2:L2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -834,7 +834,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="J1:P1"/>
+    <mergeCell ref="J2:P2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
